--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/166.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/166.xlsx
@@ -426,13 +426,13 @@
         <v>-1.202384795393654</v>
       </c>
       <c r="E2">
-        <v>-6.075561301988422</v>
+        <v>-6.963413915932272</v>
       </c>
       <c r="F2">
-        <v>-4.380702247373709</v>
+        <v>-4.359349140515838</v>
       </c>
       <c r="G2">
-        <v>-11.09423515096315</v>
+        <v>-13.40332080133157</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.549207714064369</v>
       </c>
       <c r="E3">
-        <v>-6.995172104148065</v>
+        <v>-8.102460983081597</v>
       </c>
       <c r="F3">
-        <v>-4.054342426408398</v>
+        <v>-4.250956348398374</v>
       </c>
       <c r="G3">
-        <v>-11.36885814562785</v>
+        <v>-11.56341228587974</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.827433523254057</v>
       </c>
       <c r="E4">
-        <v>-8.229339767828506</v>
+        <v>-9.464132360922004</v>
       </c>
       <c r="F4">
-        <v>-4.24713803343625</v>
+        <v>-4.121052078831496</v>
       </c>
       <c r="G4">
-        <v>-11.23735334517138</v>
+        <v>-12.14072176974555</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.959020857761854</v>
       </c>
       <c r="E5">
-        <v>-8.081525847744137</v>
+        <v>-9.231033689851181</v>
       </c>
       <c r="F5">
-        <v>-4.199607059649123</v>
+        <v>-4.322620624777924</v>
       </c>
       <c r="G5">
-        <v>-11.04391485876623</v>
+        <v>-12.49533416573012</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.932028662274307</v>
       </c>
       <c r="E6">
-        <v>-9.773667144768297</v>
+        <v>-10.39219329557996</v>
       </c>
       <c r="F6">
-        <v>-4.453162335975767</v>
+        <v>-4.566245273161806</v>
       </c>
       <c r="G6">
-        <v>-10.33781522178615</v>
+        <v>-11.51040714125047</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.723494427108758</v>
       </c>
       <c r="E7">
-        <v>-9.524832026520818</v>
+        <v>-10.69147561427289</v>
       </c>
       <c r="F7">
-        <v>-4.312685245717415</v>
+        <v>-4.104681310783598</v>
       </c>
       <c r="G7">
-        <v>-10.11617088738641</v>
+        <v>-11.73796079943781</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.334172325127467</v>
       </c>
       <c r="E8">
-        <v>-10.56046233275698</v>
+        <v>-11.47084410488899</v>
       </c>
       <c r="F8">
-        <v>-4.272623820880459</v>
+        <v>-4.806632826654528</v>
       </c>
       <c r="G8">
-        <v>-9.721471095466804</v>
+        <v>-11.18669537732946</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.7692062792636504</v>
       </c>
       <c r="E9">
-        <v>-11.75793577155326</v>
+        <v>-12.06416929784796</v>
       </c>
       <c r="F9">
-        <v>-4.591394523098984</v>
+        <v>-4.383987645295288</v>
       </c>
       <c r="G9">
-        <v>-9.913876691663706</v>
+        <v>-11.21953929962456</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.04726046806587841</v>
       </c>
       <c r="E10">
-        <v>-12.24190284570101</v>
+        <v>-13.65700568835792</v>
       </c>
       <c r="F10">
-        <v>-4.357136703351969</v>
+        <v>-4.508517608838122</v>
       </c>
       <c r="G10">
-        <v>-8.982842038017852</v>
+        <v>-10.86315576177648</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.7996267550570965</v>
       </c>
       <c r="E11">
-        <v>-12.08230130777468</v>
+        <v>-13.73249987853979</v>
       </c>
       <c r="F11">
-        <v>-4.445994483002488</v>
+        <v>-5.06129352971015</v>
       </c>
       <c r="G11">
-        <v>-8.118786341722533</v>
+        <v>-9.732372721927623</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>1.732324476737424</v>
       </c>
       <c r="E12">
-        <v>-12.59434944924399</v>
+        <v>-14.97524900046477</v>
       </c>
       <c r="F12">
-        <v>-4.734039706755572</v>
+        <v>-4.954810686926705</v>
       </c>
       <c r="G12">
-        <v>-7.38574879568941</v>
+        <v>-9.421717749613494</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>2.699105492913135</v>
       </c>
       <c r="E13">
-        <v>-13.42865285804713</v>
+        <v>-14.82015329417607</v>
       </c>
       <c r="F13">
-        <v>-4.676477539700053</v>
+        <v>-4.72239709271822</v>
       </c>
       <c r="G13">
-        <v>-6.112691750744832</v>
+        <v>-8.151835517841077</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.639062902154113</v>
       </c>
       <c r="E14">
-        <v>-14.11212638307681</v>
+        <v>-15.49508158875326</v>
       </c>
       <c r="F14">
-        <v>-4.814226696519061</v>
+        <v>-4.558567466883755</v>
       </c>
       <c r="G14">
-        <v>-5.702740275525803</v>
+        <v>-8.018758208253454</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>4.492002797158724</v>
       </c>
       <c r="E15">
-        <v>-14.52603796432589</v>
+        <v>-16.77678917256623</v>
       </c>
       <c r="F15">
-        <v>-5.093687442357505</v>
+        <v>-4.464287870031729</v>
       </c>
       <c r="G15">
-        <v>-5.95008106440137</v>
+        <v>-6.744694757464937</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>5.200297792729407</v>
       </c>
       <c r="E16">
-        <v>-16.06540213375328</v>
+        <v>-16.76679935890531</v>
       </c>
       <c r="F16">
-        <v>-4.838439976260214</v>
+        <v>-4.605557605100759</v>
       </c>
       <c r="G16">
-        <v>-4.599113640735585</v>
+        <v>-6.425035101283989</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>5.722059513261292</v>
       </c>
       <c r="E17">
-        <v>-15.85764480322938</v>
+        <v>-18.0453370109129</v>
       </c>
       <c r="F17">
-        <v>-4.324075258661256</v>
+        <v>-4.661771246569282</v>
       </c>
       <c r="G17">
-        <v>-4.20712518561264</v>
+        <v>-6.030606774098603</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>6.035445772133899</v>
       </c>
       <c r="E18">
-        <v>-17.33979623204385</v>
+        <v>-17.32526435895324</v>
       </c>
       <c r="F18">
-        <v>-4.349909461406861</v>
+        <v>-4.285242789614681</v>
       </c>
       <c r="G18">
-        <v>-4.47862633583381</v>
+        <v>-5.520253073764557</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.138519376431444</v>
       </c>
       <c r="E19">
-        <v>-17.85567093404964</v>
+        <v>-19.21141906788802</v>
       </c>
       <c r="F19">
-        <v>-4.011667094958009</v>
+        <v>-4.321858862232598</v>
       </c>
       <c r="G19">
-        <v>-3.540378003457884</v>
+        <v>-4.536497982405809</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.049645727079575</v>
       </c>
       <c r="E20">
-        <v>-18.93512328325803</v>
+        <v>-20.05622400791496</v>
       </c>
       <c r="F20">
-        <v>-4.042081375211065</v>
+        <v>-3.79915276557702</v>
       </c>
       <c r="G20">
-        <v>-3.301098392970441</v>
+        <v>-5.149865928285357</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>5.797159844457115</v>
       </c>
       <c r="E21">
-        <v>-19.22064809791565</v>
+        <v>-19.34363239501596</v>
       </c>
       <c r="F21">
-        <v>-3.721008756444449</v>
+        <v>-4.005034534584148</v>
       </c>
       <c r="G21">
-        <v>-3.565389175007078</v>
+        <v>-5.016795239788812</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.41648954424523</v>
       </c>
       <c r="E22">
-        <v>-19.78068900691825</v>
+        <v>-21.6521850454902</v>
       </c>
       <c r="F22">
-        <v>-3.5461795011743</v>
+        <v>-3.883626055400645</v>
       </c>
       <c r="G22">
-        <v>-3.323934536100334</v>
+        <v>-4.680387533724692</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.944865661726015</v>
       </c>
       <c r="E23">
-        <v>-19.55531138403051</v>
+        <v>-20.37217111095611</v>
       </c>
       <c r="F23">
-        <v>-3.458768436877535</v>
+        <v>-3.497152717150041</v>
       </c>
       <c r="G23">
-        <v>-4.037244541264939</v>
+        <v>-5.64647093299481</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.418219343258031</v>
       </c>
       <c r="E24">
-        <v>-20.38697469248718</v>
+        <v>-21.69256997669061</v>
       </c>
       <c r="F24">
-        <v>-3.399347790930247</v>
+        <v>-3.220774654875999</v>
       </c>
       <c r="G24">
-        <v>-3.863285304812856</v>
+        <v>-5.726036584485653</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.872881107578459</v>
       </c>
       <c r="E25">
-        <v>-19.5977567709044</v>
+        <v>-22.34446192399079</v>
       </c>
       <c r="F25">
-        <v>-3.114003577615944</v>
+        <v>-3.483969949109923</v>
       </c>
       <c r="G25">
-        <v>-4.242435464334506</v>
+        <v>-6.432536797475978</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.336507958725087</v>
       </c>
       <c r="E26">
-        <v>-20.31073783256805</v>
+        <v>-22.11588266997962</v>
       </c>
       <c r="F26">
-        <v>-2.990443633946316</v>
+        <v>-3.492519585494422</v>
       </c>
       <c r="G26">
-        <v>-4.527036443254572</v>
+        <v>-6.64352448578481</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.836773433708486</v>
       </c>
       <c r="E27">
-        <v>-19.82828326873887</v>
+        <v>-19.65792660504432</v>
       </c>
       <c r="F27">
-        <v>-3.05727285616603</v>
+        <v>-3.136812110210103</v>
       </c>
       <c r="G27">
-        <v>-4.356007039604744</v>
+        <v>-6.50852043869333</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.392896916842127</v>
       </c>
       <c r="E28">
-        <v>-19.55934172589733</v>
+        <v>-20.13711613911397</v>
       </c>
       <c r="F28">
-        <v>-3.170100816699683</v>
+        <v>-3.122126405256233</v>
       </c>
       <c r="G28">
-        <v>-4.697589128346745</v>
+        <v>-6.026058084527644</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.016355648346954</v>
       </c>
       <c r="E29">
-        <v>-20.57951635034531</v>
+        <v>-21.63421153215376</v>
       </c>
       <c r="F29">
-        <v>-2.743800442087608</v>
+        <v>-3.249648781126291</v>
       </c>
       <c r="G29">
-        <v>-5.96752432884779</v>
+        <v>-6.982570696643729</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.71809366777203</v>
       </c>
       <c r="E30">
-        <v>-19.73239736010046</v>
+        <v>-20.68540565806667</v>
       </c>
       <c r="F30">
-        <v>-2.871451889989773</v>
+        <v>-3.316051986454751</v>
       </c>
       <c r="G30">
-        <v>-5.969328576166693</v>
+        <v>-6.90312091424676</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.49707471782667</v>
       </c>
       <c r="E31">
-        <v>-19.32811784306568</v>
+        <v>-19.86581526131444</v>
       </c>
       <c r="F31">
-        <v>-3.029268184463314</v>
+        <v>-3.29381358799015</v>
       </c>
       <c r="G31">
-        <v>-6.218963573100976</v>
+        <v>-6.382928272569999</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.351849014733058</v>
       </c>
       <c r="E32">
-        <v>-19.76474877841125</v>
+        <v>-20.41988311310092</v>
       </c>
       <c r="F32">
-        <v>-2.852354772208447</v>
+        <v>-2.900249206503167</v>
       </c>
       <c r="G32">
-        <v>-4.786013799700679</v>
+        <v>-6.189066036335818</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.275521861585931</v>
       </c>
       <c r="E33">
-        <v>-18.52338989800663</v>
+        <v>-20.69163230982721</v>
       </c>
       <c r="F33">
-        <v>-2.844427532248715</v>
+        <v>-3.034135704594418</v>
       </c>
       <c r="G33">
-        <v>-5.607850108733672</v>
+        <v>-6.532263671300983</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.254439597203818</v>
       </c>
       <c r="E34">
-        <v>-19.14251380738731</v>
+        <v>-21.18556655526584</v>
       </c>
       <c r="F34">
-        <v>-2.480095194548912</v>
+        <v>-3.201599143651858</v>
       </c>
       <c r="G34">
-        <v>-5.526606010654418</v>
+        <v>-6.568341996587961</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.277573335411596</v>
       </c>
       <c r="E35">
-        <v>-18.29786283547663</v>
+        <v>-19.09795815162584</v>
       </c>
       <c r="F35">
-        <v>-2.639283770198182</v>
+        <v>-2.921347336708651</v>
       </c>
       <c r="G35">
-        <v>-4.995422357787278</v>
+        <v>-6.663695639755589</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.328407979889199</v>
       </c>
       <c r="E36">
-        <v>-18.14279430003198</v>
+        <v>-18.40558164669709</v>
       </c>
       <c r="F36">
-        <v>-2.737845707845555</v>
+        <v>-2.626907108469022</v>
       </c>
       <c r="G36">
-        <v>-4.630279116442283</v>
+        <v>-6.352166683419092</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.391001403416492</v>
       </c>
       <c r="E37">
-        <v>-17.2876327399495</v>
+        <v>-18.6916317643396</v>
       </c>
       <c r="F37">
-        <v>-2.346333017372023</v>
+        <v>-2.863121596874562</v>
       </c>
       <c r="G37">
-        <v>-4.631758930298338</v>
+        <v>-5.464781572708529</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.452686625913595</v>
       </c>
       <c r="E38">
-        <v>-17.30637609386725</v>
+        <v>-17.88074962310412</v>
       </c>
       <c r="F38">
-        <v>-2.593109240527629</v>
+        <v>-2.887094945169526</v>
       </c>
       <c r="G38">
-        <v>-5.229027693220409</v>
+        <v>-5.826793037973372</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.500762531976716</v>
       </c>
       <c r="E39">
-        <v>-16.8730645299693</v>
+        <v>-17.32059550225133</v>
       </c>
       <c r="F39">
-        <v>-2.511476327263345</v>
+        <v>-2.419549325548704</v>
       </c>
       <c r="G39">
-        <v>-4.921848793722514</v>
+        <v>-6.663586391752793</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.530062624009203</v>
       </c>
       <c r="E40">
-        <v>-16.97280869846225</v>
+        <v>-16.76002929026384</v>
       </c>
       <c r="F40">
-        <v>-2.277488529374913</v>
+        <v>-2.616544920664302</v>
       </c>
       <c r="G40">
-        <v>-3.873183835975277</v>
+        <v>-6.065840910273066</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.538605324659328</v>
       </c>
       <c r="E41">
-        <v>-16.24436742653641</v>
+        <v>-16.12086688339922</v>
       </c>
       <c r="F41">
-        <v>-2.43220155210715</v>
+        <v>-2.498501816551107</v>
       </c>
       <c r="G41">
-        <v>-4.966286246496152</v>
+        <v>-5.690961354497075</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.52760093498892</v>
       </c>
       <c r="E42">
-        <v>-16.4440912441707</v>
+        <v>-16.59018887260616</v>
       </c>
       <c r="F42">
-        <v>-2.407082392582365</v>
+        <v>-2.421868662861865</v>
       </c>
       <c r="G42">
-        <v>-4.80081524880676</v>
+        <v>-5.906832097476332</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.504077007657711</v>
       </c>
       <c r="E43">
-        <v>-15.64077165452803</v>
+        <v>-16.33645847395639</v>
       </c>
       <c r="F43">
-        <v>-2.482340097684048</v>
+        <v>-2.250910776702008</v>
       </c>
       <c r="G43">
-        <v>-4.499396698547197</v>
+        <v>-6.138033976847953</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.475335254170315</v>
       </c>
       <c r="E44">
-        <v>-14.4932201131923</v>
+        <v>-16.54801066569872</v>
       </c>
       <c r="F44">
-        <v>-2.409472204808763</v>
+        <v>-2.761724033785594</v>
       </c>
       <c r="G44">
-        <v>-4.755116478182661</v>
+        <v>-6.368487672927698</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.450240366911478</v>
       </c>
       <c r="E45">
-        <v>-15.58928743353483</v>
+        <v>-15.28239727850902</v>
       </c>
       <c r="F45">
-        <v>-2.664511413578174</v>
+        <v>-2.426714011110152</v>
       </c>
       <c r="G45">
-        <v>-4.993217534458123</v>
+        <v>-6.403559592370738</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.437462648013402</v>
       </c>
       <c r="E46">
-        <v>-14.34531109515378</v>
+        <v>-14.25604581551458</v>
       </c>
       <c r="F46">
-        <v>-2.315901316353897</v>
+        <v>-2.742090831551891</v>
       </c>
       <c r="G46">
-        <v>-5.011614236019853</v>
+        <v>-6.642392279210378</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.441359248490351</v>
       </c>
       <c r="E47">
-        <v>-14.60322127531263</v>
+        <v>-13.43847964664378</v>
       </c>
       <c r="F47">
-        <v>-2.693532032625644</v>
+        <v>-2.611030456666742</v>
       </c>
       <c r="G47">
-        <v>-5.267764386575422</v>
+        <v>-7.656001870242274</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.46475301770252</v>
       </c>
       <c r="E48">
-        <v>-12.24354215329179</v>
+        <v>-12.75578501914343</v>
       </c>
       <c r="F48">
-        <v>-2.930009416213147</v>
+        <v>-3.015573879412509</v>
       </c>
       <c r="G48">
-        <v>-5.601950716582691</v>
+        <v>-7.18193174901864</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.504670240778849</v>
       </c>
       <c r="E49">
-        <v>-12.7305025487586</v>
+        <v>-14.79036952062762</v>
       </c>
       <c r="F49">
-        <v>-2.668949749406193</v>
+        <v>-2.428599413002483</v>
       </c>
       <c r="G49">
-        <v>-5.05732624882611</v>
+        <v>-7.065125770756534</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>1.55487140878606</v>
       </c>
       <c r="E50">
-        <v>-12.87525069193978</v>
+        <v>-12.94494843539183</v>
       </c>
       <c r="F50">
-        <v>-2.596566470541033</v>
+        <v>-2.536083157924485</v>
       </c>
       <c r="G50">
-        <v>-5.559089083485746</v>
+        <v>-6.631520447659412</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.60740402897496</v>
       </c>
       <c r="E51">
-        <v>-11.69563755462974</v>
+        <v>-13.54291531420867</v>
       </c>
       <c r="F51">
-        <v>-2.775548202721465</v>
+        <v>-2.739409617437052</v>
       </c>
       <c r="G51">
-        <v>-6.457154014105999</v>
+        <v>-7.852158314535171</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.650471460375665</v>
       </c>
       <c r="E52">
-        <v>-11.59405029721567</v>
+        <v>-12.95511938801306</v>
       </c>
       <c r="F52">
-        <v>-3.005290085050603</v>
+        <v>-2.80413963746585</v>
       </c>
       <c r="G52">
-        <v>-6.245232751955093</v>
+        <v>-7.043782683664853</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.674910568832916</v>
       </c>
       <c r="E53">
-        <v>-11.54094488252772</v>
+        <v>-12.77983121612416</v>
       </c>
       <c r="F53">
-        <v>-2.696408042568082</v>
+        <v>-2.55795888773445</v>
       </c>
       <c r="G53">
-        <v>-5.982537652868385</v>
+        <v>-7.991989137022906</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.672514522682108</v>
       </c>
       <c r="E54">
-        <v>-10.48158084401737</v>
+        <v>-11.77983547185436</v>
       </c>
       <c r="F54">
-        <v>-2.758144066563743</v>
+        <v>-2.870352798084459</v>
       </c>
       <c r="G54">
-        <v>-6.603274873118351</v>
+        <v>-8.029401612162211</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.638219206362952</v>
       </c>
       <c r="E55">
-        <v>-10.36248650608964</v>
+        <v>-11.59346159559468</v>
       </c>
       <c r="F55">
-        <v>-2.923997668558139</v>
+        <v>-3.05644299426634</v>
       </c>
       <c r="G55">
-        <v>-6.714618451240658</v>
+        <v>-7.704219966021759</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.57214233395612</v>
       </c>
       <c r="E56">
-        <v>-9.389974070572395</v>
+        <v>-10.54710333443435</v>
       </c>
       <c r="F56">
-        <v>-3.165858860405178</v>
+        <v>-3.151233336276095</v>
       </c>
       <c r="G56">
-        <v>-6.887915578584887</v>
+        <v>-9.20070572941175</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.476282734989927</v>
       </c>
       <c r="E57">
-        <v>-10.2671123150141</v>
+        <v>-11.05855824580865</v>
       </c>
       <c r="F57">
-        <v>-2.947721583171422</v>
+        <v>-3.290611334629132</v>
       </c>
       <c r="G57">
-        <v>-6.561744079328194</v>
+        <v>-7.926754837171567</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.357318189164525</v>
       </c>
       <c r="E58">
-        <v>-10.01119013494461</v>
+        <v>-10.13607639112815</v>
       </c>
       <c r="F58">
-        <v>-2.891174571607698</v>
+        <v>-3.153453691969541</v>
       </c>
       <c r="G58">
-        <v>-6.917266875336066</v>
+        <v>-8.354586568848202</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.223258297190239</v>
       </c>
       <c r="E59">
-        <v>-9.130750632951321</v>
+        <v>-10.02516953420629</v>
       </c>
       <c r="F59">
-        <v>-3.03820107767935</v>
+        <v>-2.769155573793793</v>
       </c>
       <c r="G59">
-        <v>-6.353600149637596</v>
+        <v>-8.557483283859053</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.082064231585835</v>
       </c>
       <c r="E60">
-        <v>-8.570093851483676</v>
+        <v>-9.103625073645375</v>
       </c>
       <c r="F60">
-        <v>-3.183661298600633</v>
+        <v>-3.475497914315279</v>
       </c>
       <c r="G60">
-        <v>-7.07386561098021</v>
+        <v>-8.549074498189304</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.9435336434493324</v>
       </c>
       <c r="E61">
-        <v>-9.117527488848923</v>
+        <v>-9.726946878431162</v>
       </c>
       <c r="F61">
-        <v>-3.127016097270153</v>
+        <v>-3.566374127155026</v>
       </c>
       <c r="G61">
-        <v>-6.643607249423291</v>
+        <v>-8.826759747477833</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.8152763439741876</v>
       </c>
       <c r="E62">
-        <v>-9.261492206026771</v>
+        <v>-10.23897690600444</v>
       </c>
       <c r="F62">
-        <v>-3.171936331855677</v>
+        <v>-3.525588156861756</v>
       </c>
       <c r="G62">
-        <v>-7.10920568461193</v>
+        <v>-9.224856159120732</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.7047440170814996</v>
       </c>
       <c r="E63">
-        <v>-8.397482007733306</v>
+        <v>-9.15372811006624</v>
       </c>
       <c r="F63">
-        <v>-3.167342000994987</v>
+        <v>-3.267853480624267</v>
       </c>
       <c r="G63">
-        <v>-7.386106334607651</v>
+        <v>-9.497247846091966</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.6189607710724528</v>
       </c>
       <c r="E64">
-        <v>-7.672654458065589</v>
+        <v>-8.89597642649766</v>
       </c>
       <c r="F64">
-        <v>-3.014980781547177</v>
+        <v>-3.169368352713792</v>
       </c>
       <c r="G64">
-        <v>-7.345340276837065</v>
+        <v>-9.428659963609345</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.5611003311959809</v>
       </c>
       <c r="E65">
-        <v>-8.944788847826338</v>
+        <v>-9.52348706974054</v>
       </c>
       <c r="F65">
-        <v>-2.945993760017677</v>
+        <v>-3.583969099875558</v>
       </c>
       <c r="G65">
-        <v>-7.65379373636758</v>
+        <v>-9.297655055529306</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.534469590615732</v>
       </c>
       <c r="E66">
-        <v>-7.997142263085208</v>
+        <v>-9.557043062137378</v>
       </c>
       <c r="F66">
-        <v>-3.201573804357211</v>
+        <v>-3.639381386150869</v>
       </c>
       <c r="G66">
-        <v>-7.540093049821311</v>
+        <v>-9.045758955991701</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.5396737627624265</v>
       </c>
       <c r="E67">
-        <v>-8.513777748724289</v>
+        <v>-8.982076302805496</v>
       </c>
       <c r="F67">
-        <v>-3.352059124148183</v>
+        <v>-3.329553079383873</v>
       </c>
       <c r="G67">
-        <v>-7.535004741327451</v>
+        <v>-9.087498314150832</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.5748237900337296</v>
       </c>
       <c r="E68">
-        <v>-7.646597618625453</v>
+        <v>-8.834796742654031</v>
       </c>
       <c r="F68">
-        <v>-3.330839048587209</v>
+        <v>-3.142204628852174</v>
       </c>
       <c r="G68">
-        <v>-7.708874593049974</v>
+        <v>-8.89586407506458</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.6377647332695944</v>
       </c>
       <c r="E69">
-        <v>-8.389480194161752</v>
+        <v>-8.161643609887841</v>
       </c>
       <c r="F69">
-        <v>-3.045348342475729</v>
+        <v>-3.625196132266278</v>
       </c>
       <c r="G69">
-        <v>-7.745396531439214</v>
+        <v>-9.457296182524042</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.7220696580054159</v>
       </c>
       <c r="E70">
-        <v>-7.670784198300421</v>
+        <v>-8.928060664842004</v>
       </c>
       <c r="F70">
-        <v>-3.090289957091112</v>
+        <v>-3.361236699928154</v>
       </c>
       <c r="G70">
-        <v>-7.462245571465349</v>
+        <v>-8.386662444578199</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.8213348640690133</v>
       </c>
       <c r="E71">
-        <v>-8.025725991021623</v>
+        <v>-8.740083708783606</v>
       </c>
       <c r="F71">
-        <v>-3.439961929131691</v>
+        <v>-3.543571137531571</v>
       </c>
       <c r="G71">
-        <v>-8.435549270556617</v>
+        <v>-8.48958730539414</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.9275221007897464</v>
       </c>
       <c r="E72">
-        <v>-8.286181173572784</v>
+        <v>-10.11664470916123</v>
       </c>
       <c r="F72">
-        <v>-3.121819958161596</v>
+        <v>-3.136231681992095</v>
       </c>
       <c r="G72">
-        <v>-8.023128128365292</v>
+        <v>-9.159595374905079</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>1.030780093610691</v>
       </c>
       <c r="E73">
-        <v>-9.118614322610764</v>
+        <v>-8.637844351112433</v>
       </c>
       <c r="F73">
-        <v>-3.232251771645188</v>
+        <v>-3.173665738715337</v>
       </c>
       <c r="G73">
-        <v>-7.970053462279695</v>
+        <v>-8.943807395564304</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>1.123340360189171</v>
       </c>
       <c r="E74">
-        <v>-8.728051553345226</v>
+        <v>-8.36262181482226</v>
       </c>
       <c r="F74">
-        <v>-3.09536415084418</v>
+        <v>-3.597190668710604</v>
       </c>
       <c r="G74">
-        <v>-7.453783817066972</v>
+        <v>-9.919501308534928</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.19768638602147</v>
       </c>
       <c r="E75">
-        <v>-8.924967717094765</v>
+        <v>-10.18288269847143</v>
       </c>
       <c r="F75">
-        <v>-3.023411639988019</v>
+        <v>-3.512243058965305</v>
       </c>
       <c r="G75">
-        <v>-8.253816873178325</v>
+        <v>-9.046252227277051</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.248968400165785</v>
       </c>
       <c r="E76">
-        <v>-9.648604278098464</v>
+        <v>-9.816329898394558</v>
       </c>
       <c r="F76">
-        <v>-3.49143712250122</v>
+        <v>-3.559157179298368</v>
       </c>
       <c r="G76">
-        <v>-8.025733527704698</v>
+        <v>-9.740390863223737</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.274583618899008</v>
       </c>
       <c r="E77">
-        <v>-10.35822974052243</v>
+        <v>-9.884918165714735</v>
       </c>
       <c r="F77">
-        <v>-3.213132481981046</v>
+        <v>-3.066261970942064</v>
       </c>
       <c r="G77">
-        <v>-8.101558262736164</v>
+        <v>-9.00369516436972</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.273304679020076</v>
       </c>
       <c r="E78">
-        <v>-10.18494768261893</v>
+        <v>-10.78294173227981</v>
       </c>
       <c r="F78">
-        <v>-3.356930603544074</v>
+        <v>-3.131049796236777</v>
       </c>
       <c r="G78">
-        <v>-8.602278275550931</v>
+        <v>-9.900876179330988</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.246328450082057</v>
       </c>
       <c r="E79">
-        <v>-10.92437050401337</v>
+        <v>-11.25018515191723</v>
       </c>
       <c r="F79">
-        <v>-3.636242481026468</v>
+        <v>-3.452687006162247</v>
       </c>
       <c r="G79">
-        <v>-7.689395343096902</v>
+        <v>-8.322590146211144</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.195674912249239</v>
       </c>
       <c r="E80">
-        <v>-11.35661787651951</v>
+        <v>-12.32259119556968</v>
       </c>
       <c r="F80">
-        <v>-3.631082767153966</v>
+        <v>-3.789294196253409</v>
       </c>
       <c r="G80">
-        <v>-8.293305060370752</v>
+        <v>-8.778975333163993</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.124282193870772</v>
       </c>
       <c r="E81">
-        <v>-11.74408769803781</v>
+        <v>-13.15596173872725</v>
       </c>
       <c r="F81">
-        <v>-3.656639029511413</v>
+        <v>-3.375119465982896</v>
       </c>
       <c r="G81">
-        <v>-8.363895822904631</v>
+        <v>-8.966372073959977</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.03497540685849</v>
       </c>
       <c r="E82">
-        <v>-12.6778952662115</v>
+        <v>-13.41627653858417</v>
       </c>
       <c r="F82">
-        <v>-3.273139890970004</v>
+        <v>-3.084887936213548</v>
       </c>
       <c r="G82">
-        <v>-7.637754143229811</v>
+        <v>-8.67251480971211</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.9293572029031893</v>
       </c>
       <c r="E83">
-        <v>-12.49350033309317</v>
+        <v>-13.79128399963336</v>
       </c>
       <c r="F83">
-        <v>-3.267710947091877</v>
+        <v>-3.514073823003554</v>
       </c>
       <c r="G83">
-        <v>-7.982656709147701</v>
+        <v>-9.588370612060405</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.809448391683</v>
       </c>
       <c r="E84">
-        <v>-14.14781075825725</v>
+        <v>-15.24210744526277</v>
       </c>
       <c r="F84">
-        <v>-3.432820999158975</v>
+        <v>-3.533276257228257</v>
       </c>
       <c r="G84">
-        <v>-8.056412353217123</v>
+        <v>-9.134037963341905</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.6754565723406077</v>
       </c>
       <c r="E85">
-        <v>-14.89903931138968</v>
+        <v>-15.04964729993678</v>
       </c>
       <c r="F85">
-        <v>-3.621736526694</v>
+        <v>-3.696616517934851</v>
       </c>
       <c r="G85">
-        <v>-7.807479191937166</v>
+        <v>-9.301501909445939</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.5278273725270513</v>
       </c>
       <c r="E86">
-        <v>-16.56103908541879</v>
+        <v>-16.82845906099375</v>
       </c>
       <c r="F86">
-        <v>-3.656324663887198</v>
+        <v>-3.938688342668643</v>
       </c>
       <c r="G86">
-        <v>-7.62672009494742</v>
+        <v>-9.529674639649127</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.365211997090659</v>
       </c>
       <c r="E87">
-        <v>-17.37850562786142</v>
+        <v>-18.47340460190997</v>
       </c>
       <c r="F87">
-        <v>-3.887856133900783</v>
+        <v>-4.053361320593782</v>
       </c>
       <c r="G87">
-        <v>-7.741331181516989</v>
+        <v>-9.582368592997707</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.184995012488545</v>
       </c>
       <c r="E88">
-        <v>-18.94128200790846</v>
+        <v>-18.97707506646509</v>
       </c>
       <c r="F88">
-        <v>-3.777374433680854</v>
+        <v>-3.492485535817241</v>
       </c>
       <c r="G88">
-        <v>-8.829620058823764</v>
+        <v>-8.936606959016389</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.01454299719475408</v>
       </c>
       <c r="E89">
-        <v>-19.67988970398152</v>
+        <v>-21.29979278363532</v>
       </c>
       <c r="F89">
-        <v>-3.583908919050771</v>
+        <v>-3.848857375733087</v>
       </c>
       <c r="G89">
-        <v>-8.309589633878428</v>
+        <v>-9.342072645029708</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2376834374920914</v>
       </c>
       <c r="E90">
-        <v>-20.43888911851112</v>
+        <v>-22.26951567916384</v>
       </c>
       <c r="F90">
-        <v>-3.500207685860923</v>
+        <v>-3.689308506988055</v>
       </c>
       <c r="G90">
-        <v>-7.991939478839818</v>
+        <v>-9.08923304001341</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.4861672839037848</v>
       </c>
       <c r="E91">
-        <v>-22.8500162337331</v>
+        <v>-23.89956254059483</v>
       </c>
       <c r="F91">
-        <v>-3.382343540516173</v>
+        <v>-3.449324798503769</v>
       </c>
       <c r="G91">
-        <v>-8.105646786477164</v>
+        <v>-9.764263207107422</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.7609065192295992</v>
       </c>
       <c r="E92">
-        <v>-24.86079001888496</v>
+        <v>-23.81164674620991</v>
       </c>
       <c r="F92">
-        <v>-3.223851795469697</v>
+        <v>-3.22605948151582</v>
       </c>
       <c r="G92">
-        <v>-8.357678618381881</v>
+        <v>-10.07634833509452</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.060943580301319</v>
       </c>
       <c r="E93">
-        <v>-27.49331875681595</v>
+        <v>-28.33743084031972</v>
       </c>
       <c r="F93">
-        <v>-3.588067730784716</v>
+        <v>-3.409481925083144</v>
       </c>
       <c r="G93">
-        <v>-9.046728945834706</v>
+        <v>-9.125854294768827</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.379287644350387</v>
       </c>
       <c r="E94">
-        <v>-29.17160292337664</v>
+        <v>-29.45805607520584</v>
       </c>
       <c r="F94">
-        <v>-3.174100465989125</v>
+        <v>-3.182954173909389</v>
       </c>
       <c r="G94">
-        <v>-8.504921752332045</v>
+        <v>-9.021505899371</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.709093835481122</v>
       </c>
       <c r="E95">
-        <v>-30.61192936625627</v>
+        <v>-31.94875979992761</v>
       </c>
       <c r="F95">
-        <v>-3.457987669861223</v>
+        <v>-2.923528891607169</v>
       </c>
       <c r="G95">
-        <v>-8.102270030027109</v>
+        <v>-9.059997612356106</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.038862987761499</v>
       </c>
       <c r="E96">
-        <v>-33.85524282868282</v>
+        <v>-33.24451244587536</v>
       </c>
       <c r="F96">
-        <v>-3.225228035910214</v>
+        <v>-2.550053819657534</v>
       </c>
       <c r="G96">
-        <v>-8.623780268828499</v>
+        <v>-9.383408116633047</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.35435803491468</v>
       </c>
       <c r="E97">
-        <v>-36.25203053095952</v>
+        <v>-36.64836031187382</v>
       </c>
       <c r="F97">
-        <v>-3.126632840438616</v>
+        <v>-2.465255870121244</v>
       </c>
       <c r="G97">
-        <v>-8.875490977815904</v>
+        <v>-10.55257362146422</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.64745539363817</v>
       </c>
       <c r="E98">
-        <v>-38.25592782833073</v>
+        <v>-38.96538573721641</v>
       </c>
       <c r="F98">
-        <v>-3.332026828023789</v>
+        <v>-2.908243753964305</v>
       </c>
       <c r="G98">
-        <v>-9.082992661671883</v>
+        <v>-10.66370863521755</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.903889335251114</v>
       </c>
       <c r="E99">
-        <v>-41.50863108161218</v>
+        <v>-41.66250636415581</v>
       </c>
       <c r="F99">
-        <v>-3.039560689207756</v>
+        <v>-2.739949661154216</v>
       </c>
       <c r="G99">
-        <v>-8.770099760573206</v>
+        <v>-10.36059508564188</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.127439842877159</v>
       </c>
       <c r="E100">
-        <v>-44.29188781265147</v>
+        <v>-43.88677279216229</v>
       </c>
       <c r="F100">
-        <v>-3.0649577891207</v>
+        <v>-2.485185225361135</v>
       </c>
       <c r="G100">
-        <v>-9.797603711233423</v>
+        <v>-11.36489211207181</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.308567436795064</v>
       </c>
       <c r="E101">
-        <v>-45.75291164598316</v>
+        <v>-46.87804044826991</v>
       </c>
       <c r="F101">
-        <v>-3.366558743656988</v>
+        <v>-2.061261993328134</v>
       </c>
       <c r="G101">
-        <v>-10.20802197337349</v>
+        <v>-11.21283544490754</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.468323884660193</v>
       </c>
       <c r="E102">
-        <v>-48.70718053732963</v>
+        <v>-49.1467674340837</v>
       </c>
       <c r="F102">
-        <v>-2.554170663184719</v>
+        <v>-2.236343849691796</v>
       </c>
       <c r="G102">
-        <v>-10.1476310016461</v>
+        <v>-11.53211438835147</v>
       </c>
     </row>
   </sheetData>
